--- a/data/credit_bond_2026-09-10.xlsx
+++ b/data/credit_bond_2026-09-10.xlsx
@@ -700,7 +700,11 @@
           <t>09-10 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>102683589.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -779,7 +783,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X3" s="3"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>1.99%~2.09%</t>
+        </is>
+      </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>AAA</t>

--- a/data/credit_bond_2026-09-10.xlsx
+++ b/data/credit_bond_2026-09-10.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-10" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-11" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-10</t>
+          <t>数据来源：DM    2026-09-11</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,9 @@
       <c r="E3" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>1.60 ~ 2.40</t>
@@ -743,7 +745,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>2.1200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -753,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.45</t>
+          <t>C+ 33.23</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -776,8 +778,12 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
+      <c r="U3" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>1.3</v>
+      </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
           <t>6+</t>

--- a/data/credit_bond_2026-09-10.xlsx
+++ b/data/credit_bond_2026-09-10.xlsx
@@ -721,8 +721,12 @@
           <t>1.60 ~ 2.40</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>52.74</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2.02</t>
